--- a/data/trans_bre/P2A_senso_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,22</t>
+          <t>-2,43; 0,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,95</t>
+          <t>-1,65; 1,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,15</t>
+          <t>-0,9; 1,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,48</t>
+          <t>-1,71; 1,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,69; 26,56</t>
+          <t>-79,92; 25,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 119,78</t>
+          <t>-52,23; 118,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-72,18; 310,96</t>
+          <t>-66,52; 349,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,32; 109,99</t>
+          <t>-54,57; 99,6</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,39</t>
+          <t>-0,97; 1,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,73</t>
+          <t>-0,89; 1,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,27</t>
+          <t>-0,7; 1,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,63</t>
+          <t>-0,33; 2,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 153,14</t>
+          <t>-46,35; 151,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,54; 179,37</t>
+          <t>-41,77; 149,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 244,83</t>
+          <t>-57,92; 267,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 286,95</t>
+          <t>-12,8; 278,18</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>631,06%</t>
+          <t>631,07%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,76</t>
+          <t>-0,89; 1,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,61</t>
+          <t>-0,87; 1,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,86</t>
+          <t>-1,3; 0,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 53,86</t>
+          <t>0,27; 58,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 328,36</t>
+          <t>-52,36; 316,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-65,56; 301,59</t>
+          <t>-59,45; 285,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-78,85; 247,12</t>
+          <t>-81,5; 297,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 2136,14</t>
+          <t>6,03; 2431,45</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,71</t>
+          <t>-0,61; 1,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,3</t>
+          <t>-0,45; 2,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,76</t>
+          <t>-1,16; 0,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,82</t>
+          <t>-0,5; 1,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 180,99</t>
+          <t>-35,45; 202,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 220,65</t>
+          <t>-22,46; 213,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,27; 119,11</t>
+          <t>-65,12; 134,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 148,37</t>
+          <t>-23,24; 158,71</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,71</t>
+          <t>-0,51; 0,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,13</t>
+          <t>-0,17; 1,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,57</t>
+          <t>-0,49; 0,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 23,16</t>
+          <t>0,47; 23,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 56,33</t>
+          <t>-28,66; 58,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 80,11</t>
+          <t>-8,54; 90,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 73,93</t>
+          <t>-38,88; 69,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,06; 1225,76</t>
+          <t>19,72; 1180,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_senso_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-1,62%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,33</t>
+          <t>-2,46; 0,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,9</t>
+          <t>-1,62; 1,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,25</t>
+          <t>-0,81; 1,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,54</t>
+          <t>-0,92; 2,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-79,92; 25,27</t>
+          <t>-78,93; 24,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 118,83</t>
+          <t>-47,93; 104,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-66,52; 349,67</t>
+          <t>-66,45; 313,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-54,57; 99,6</t>
+          <t>-35,0; 158,9</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,33</t>
+          <t>-0,88; 1,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,61</t>
+          <t>-0,87; 1,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,33</t>
+          <t>-0,63; 1,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,72</t>
+          <t>-0,78; 2,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,35; 151,99</t>
+          <t>-45,37; 174,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,77; 149,0</t>
+          <t>-41,99; 183,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,92; 267,42</t>
+          <t>-49,67; 299,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 278,18</t>
+          <t>-27,97; 132,91</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,82</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>631,07%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,75</t>
+          <t>-0,79; 1,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,59</t>
+          <t>-0,83; 1,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,87</t>
+          <t>-1,12; 0,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 58,48</t>
+          <t>-1,2; 2,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,36; 316,63</t>
+          <t>-51,66; 354,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,45; 285,78</t>
+          <t>-64,69; 323,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-81,5; 297,6</t>
+          <t>-76,75; 300,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 2431,45</t>
+          <t>-24,57; 100,95</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>57,41%</t>
         </is>
       </c>
     </row>
@@ -965,37 +965,37 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,33</t>
+          <t>-0,27; 2,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,85</t>
+          <t>-1,21; 0,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,81</t>
+          <t>-0,08; 2,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,45; 202,54</t>
+          <t>-35,25; 206,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 213,61</t>
+          <t>-17,5; 215,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,12; 134,61</t>
+          <t>-65,06; 114,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 158,71</t>
+          <t>-5,29; 169,23</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>273,33%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,74</t>
+          <t>-0,48; 0,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,2</t>
+          <t>-0,2; 1,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,54</t>
+          <t>-0,43; 0,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 23,23</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 58,47</t>
+          <t>-26,27; 57,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 90,33</t>
+          <t>-11,01; 86,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-38,88; 69,91</t>
+          <t>-34,58; 78,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,72; 1180,41</t>
+          <t>-0,19; 70,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_senso_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
